--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Back_Summary.xlsx
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.98685</v>
+        <v>17.27249</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0226</v>
+        <v>16.91876</v>
       </c>
       <c r="E2" t="n">
-        <v>16.74594</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43.16276</v>
+        <v>17.03666</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05082</v>
+        <v>0.05108</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85901</v>
+        <v>1.81557</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +482,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.41389</v>
+        <v>17.16622</v>
       </c>
       <c r="D3" t="n">
-        <v>16.82463</v>
+        <v>16.71645</v>
       </c>
       <c r="E3" t="n">
-        <v>16.85018</v>
+        <v>16.97812</v>
       </c>
       <c r="F3" t="n">
-        <v>43.69116</v>
+        <v>43.11013</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05189</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82402</v>
+        <v>1.83854</v>
       </c>
     </row>
     <row r="4">
@@ -499,23 +506,25 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>17.08652</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>17.03169</v>
+        <v>16.80428</v>
       </c>
       <c r="E4" t="n">
-        <v>17.35329</v>
+        <v>16.88604</v>
       </c>
       <c r="F4" t="n">
-        <v>42.67751</v>
+        <v>42.75187</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05089</v>
+        <v>0.05052</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83588</v>
+        <v>1.8503</v>
       </c>
     </row>
     <row r="5">
@@ -524,23 +533,25 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>17.17928</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,5</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>16.92946</v>
+        <v>16.8888</v>
       </c>
       <c r="E5" t="n">
-        <v>16.87897</v>
+        <v>16.98551</v>
       </c>
       <c r="F5" t="n">
-        <v>43.95456</v>
+        <v>44.19469</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05035</v>
+        <v>0.05153</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84936</v>
+        <v>1.85564</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +561,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8937</v>
+        <v>17.13749</v>
       </c>
       <c r="D6" t="n">
-        <v>16.56938</v>
+        <v>16.75235</v>
       </c>
       <c r="E6" t="n">
-        <v>17.08216</v>
+        <v>16.88026</v>
       </c>
       <c r="F6" t="n">
-        <v>43.26664</v>
+        <v>42.92424</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05133</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.869</v>
+        <v>0.05181</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +586,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.86162</v>
+        <v>17.16501</v>
       </c>
       <c r="D7" t="n">
-        <v>17.0813</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.87835</v>
+        <v>16.72705</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16.48 </t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>42.38775</v>
+        <v>43.89895</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05047</v>
+        <v>0.05135</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85104</v>
+        <v>1.84962</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +613,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.19734</v>
+        <v>16.99941</v>
       </c>
       <c r="D8" t="n">
-        <v>17.00691</v>
+        <v>16.8041</v>
       </c>
       <c r="E8" t="n">
-        <v>16.60401</v>
+        <v>16.92903</v>
       </c>
       <c r="F8" t="n">
-        <v>42.72994</v>
+        <v>43.41649</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0524</v>
+        <v>0.05111</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9013</v>
+        <v>1.8628</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +638,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.18692</v>
+        <v>16.90699</v>
       </c>
       <c r="D9" t="n">
-        <v>17.10662</v>
+        <v>16.44583</v>
       </c>
       <c r="E9" t="n">
-        <v>17.2962</v>
+        <v>16.7422</v>
       </c>
       <c r="F9" t="n">
-        <v>43.3032</v>
+        <v>43.73156</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05136</v>
+        <v>0.05109</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8858</v>
+        <v>1.84192</v>
       </c>
     </row>
     <row r="10">
@@ -650,22 +663,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.1473</v>
+        <v>17.27521</v>
       </c>
       <c r="D10" t="n">
-        <v>16.84961</v>
+        <v>16.742</v>
       </c>
       <c r="E10" t="n">
-        <v>17.02566</v>
+        <v>16.78897</v>
       </c>
       <c r="F10" t="n">
-        <v>44.06441</v>
+        <v>43.39774</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0508</v>
+        <v>0.05168</v>
       </c>
       <c r="H10" t="n">
-        <v>1.87204</v>
+        <v>1.87299</v>
       </c>
     </row>
     <row r="11">
@@ -692,10 +705,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6203</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16631</v>
+        <v>1.13184</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +718,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6236699999999999</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1273</v>
+        <v>1.14581</v>
       </c>
     </row>
     <row r="14">
@@ -718,10 +731,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.61447</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.13679</v>
+        <v>1.14551</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +744,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.61743</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13544</v>
+        <v>1.12171</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +757,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6224499999999999</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1.12532</v>
+        <v>1.12067</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +770,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.62048</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1.14281</v>
+        <v>1.11215</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +783,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.62747</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.14507</v>
+        <v>1.15645</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +796,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.62922</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12044</v>
+        <v>1.13787</v>
       </c>
     </row>
     <row r="20">
@@ -796,10 +809,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6323</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1452</v>
+        <v>1.10822</v>
       </c>
     </row>
   </sheetData>
